--- a/2.xlsx
+++ b/2.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\数据验证\_analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software\GitHubDesktop\Repository\APS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{6F149C8C-F1FF-4F32-8F75-8A1536DDE3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38A6163-8C95-4719-BE77-618C5869E3DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{8B0E0632-0459-4DC0-AC21-10667FF23463}"/>
   </bookViews>
   <sheets>
-    <sheet name="issue5_order_version_conflicts_" sheetId="1" r:id="rId1"/>
+    <sheet name="同一订单存在双版本" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -1747,7 +1747,7 @@
     <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
     <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -1759,13 +1759,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -11125,11 +11118,11 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A2:A149">
-    <cfRule type="expression" dxfId="2" priority="2">
-      <formula>MOD(ROW()-2,4)&lt;2</formula>
-    </cfRule>
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>MOD(ROW()-2,4)&gt;=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD(ROW()-2,4)&lt;2</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2.xlsx
+++ b/2.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Software\GitHubDesktop\Repository\APS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38A6163-8C95-4719-BE77-618C5869E3DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7751DE3D-8448-43A9-841D-6732296CACFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{8B0E0632-0459-4DC0-AC21-10667FF23463}"/>
   </bookViews>
   <sheets>
-    <sheet name="同一订单存在双版本" sheetId="1" r:id="rId1"/>
+    <sheet name="不同版本对应的状态字段、交期字段、备注字段值不同" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
